--- a/input/align_popProjections.xlsx
+++ b/input/align_popProjections.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61F86D8D-5BC8-47CE-B8A3-2D9D0B875A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF857A8-7327-47E1-90E1-CF43A722D205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{27F44677-18C3-4294-AFAC-F09705E769BF}"/>
   </bookViews>
